--- a/assets/docs/lop4/Hoat dong trai nghiem - Lop 4.xlsx
+++ b/assets/docs/lop4/Hoat dong trai nghiem - Lop 4.xlsx
@@ -1490,7 +1490,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS khảo sát, tổng hợp được số liệu về cảnh quan trường lớp và chỉ ra việc cần làm.</t>
+          <t>Năng lực số 1.1 CB2c: HS khảo sát, tổng hợp được số liệu về cảnh quan trường lớp và chỉ ra việc cần làm.
+Học tập và làm theo Bác: Điều 4 “Giữ gìn vệ sinh thật tốt” (mạch 4): khi lập kế hoạch giữ trường học xanh, sạch, đẹp, mỗi tổ ghi rõ việc, người làm, thời gian; HS thực hiện ở tiết sinh hoạt lớp cuối tuần.</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2348,7 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr"/>
@@ -2377,7 +2378,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr"/>
@@ -2412,7 +2413,7 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr"/>
@@ -2447,7 +2448,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr"/>
@@ -2477,7 +2478,7 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr"/>
@@ -2512,7 +2513,7 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Trước Tết</t>
+          <t>Chủ đề: Mái ấm gia đình</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr"/>
@@ -3279,7 +3280,7 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr"/>
@@ -3313,7 +3314,7 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr"/>
@@ -3335,7 +3336,8 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí cảnh quan địa phương trên bản đồ số và mô tả đặc điểm của nó.</t>
+          <t>Năng lực số 1.1 CB2c: HS xác định được vị trí cảnh quan địa phương trên bản đồ số và mô tả đặc điểm của nó.
+QPAN: Tổ chức tham quan di tích lịch sử, nhà truyền thống ở địa phương hoặc xem tư liệu thay thế; giáo dục nhận biết chủ quyền lãnh thổ; có ý thức chấp hành pháp luật, nhất là pháp luật giao thông.</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3349,7 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr"/>
@@ -3369,7 +3371,8 @@
       </c>
       <c r="H87" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.</t>
+          <t>Năng lực số 2.1 CB2a: HS nhập, đọc số liệu thi đua và nhận xét dựa trên kết quả thật của tổ mình.
+KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3384,7 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr"/>
@@ -3416,7 +3419,7 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr"/>
@@ -3451,7 +3454,7 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr"/>
@@ -3486,7 +3489,7 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr"/>
@@ -3521,7 +3524,7 @@
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr"/>
@@ -3556,7 +3559,7 @@
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr"/>
@@ -3591,7 +3594,7 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr"/>
@@ -3626,7 +3629,7 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr"/>
@@ -3661,7 +3664,7 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Chủ đề: Kết nối cộng đồng</t>
+          <t>Chủ đề: Quê hương em tươi đẹp</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr"/>
